--- a/artfynd/A 58744-2022 artfynd.xlsx
+++ b/artfynd/A 58744-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131802</v>
+        <v>122131742</v>
       </c>
       <c r="B2" t="n">
-        <v>79713</v>
+        <v>90740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>885</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tajgaporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inonotopsis subiculosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Peck) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570568</v>
+        <v>570510</v>
       </c>
       <c r="R2" t="n">
-        <v>7108432</v>
+        <v>7108431</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131760</v>
+        <v>122131776</v>
       </c>
       <c r="B3" t="n">
-        <v>78632</v>
+        <v>97103</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570496</v>
+        <v>570525</v>
       </c>
       <c r="R3" t="n">
-        <v>7108437</v>
+        <v>7108433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>122132202</v>
       </c>
       <c r="B4" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131821</v>
+        <v>122131802</v>
       </c>
       <c r="B5" t="n">
-        <v>78632</v>
+        <v>79720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570563</v>
+        <v>570568</v>
       </c>
       <c r="R5" t="n">
-        <v>7108426</v>
+        <v>7108432</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131742</v>
+        <v>122131821</v>
       </c>
       <c r="B6" t="n">
-        <v>90731</v>
+        <v>78639</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>885</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tajgaporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inonotopsis subiculosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570510</v>
+        <v>570563</v>
       </c>
       <c r="R6" t="n">
-        <v>7108431</v>
+        <v>7108426</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131776</v>
+        <v>122131760</v>
       </c>
       <c r="B7" t="n">
-        <v>97094</v>
+        <v>78639</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570525</v>
+        <v>570496</v>
       </c>
       <c r="R7" t="n">
-        <v>7108433</v>
+        <v>7108437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58744-2022 artfynd.xlsx
+++ b/artfynd/A 58744-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131742</v>
+        <v>122131802</v>
       </c>
       <c r="B2" t="n">
-        <v>90765</v>
+        <v>79726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>885</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tajgaporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Inonotopsis subiculosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570510</v>
+        <v>570568</v>
       </c>
       <c r="R2" t="n">
-        <v>7108431</v>
+        <v>7108432</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131821</v>
+        <v>122131742</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>90765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>885</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgaporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inonotopsis subiculosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570563</v>
+        <v>570510</v>
       </c>
       <c r="R3" t="n">
-        <v>7108426</v>
+        <v>7108431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131760</v>
+        <v>122131776</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570496</v>
+        <v>570525</v>
       </c>
       <c r="R4" t="n">
-        <v>7108437</v>
+        <v>7108433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131802</v>
+        <v>122131821</v>
       </c>
       <c r="B6" t="n">
-        <v>79726</v>
+        <v>78645</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570568</v>
+        <v>570563</v>
       </c>
       <c r="R6" t="n">
-        <v>7108432</v>
+        <v>7108426</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131776</v>
+        <v>122131760</v>
       </c>
       <c r="B7" t="n">
-        <v>97129</v>
+        <v>78645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570525</v>
+        <v>570496</v>
       </c>
       <c r="R7" t="n">
-        <v>7108433</v>
+        <v>7108437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58744-2022 artfynd.xlsx
+++ b/artfynd/A 58744-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131742</v>
+        <v>122131776</v>
       </c>
       <c r="B3" t="n">
-        <v>90765</v>
+        <v>97129</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>885</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tajgaporing</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inonotopsis subiculosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570510</v>
+        <v>570525</v>
       </c>
       <c r="R3" t="n">
-        <v>7108431</v>
+        <v>7108433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131776</v>
+        <v>122131742</v>
       </c>
       <c r="B4" t="n">
-        <v>97129</v>
+        <v>90765</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>885</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tajgaporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Inonotopsis subiculosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570525</v>
+        <v>570510</v>
       </c>
       <c r="R4" t="n">
-        <v>7108433</v>
+        <v>7108431</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 58744-2022 artfynd.xlsx
+++ b/artfynd/A 58744-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131802</v>
+        <v>122131821</v>
       </c>
       <c r="B2" t="n">
-        <v>79726</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570568</v>
+        <v>570563</v>
       </c>
       <c r="R2" t="n">
-        <v>7108432</v>
+        <v>7108426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131776</v>
+        <v>122131802</v>
       </c>
       <c r="B3" t="n">
-        <v>97129</v>
+        <v>79727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570525</v>
+        <v>570568</v>
       </c>
       <c r="R3" t="n">
-        <v>7108433</v>
+        <v>7108432</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>122131742</v>
       </c>
       <c r="B4" t="n">
-        <v>90765</v>
+        <v>90775</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131821</v>
+        <v>122131760</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570563</v>
+        <v>570496</v>
       </c>
       <c r="R6" t="n">
-        <v>7108426</v>
+        <v>7108437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131760</v>
+        <v>122131776</v>
       </c>
       <c r="B7" t="n">
-        <v>78645</v>
+        <v>97139</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570496</v>
+        <v>570525</v>
       </c>
       <c r="R7" t="n">
-        <v>7108437</v>
+        <v>7108433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58744-2022 artfynd.xlsx
+++ b/artfynd/A 58744-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131821</v>
+        <v>122131742</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>90775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>885</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgaporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inonotopsis subiculosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570563</v>
+        <v>570510</v>
       </c>
       <c r="R2" t="n">
-        <v>7108426</v>
+        <v>7108431</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131802</v>
+        <v>122132202</v>
       </c>
       <c r="B3" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,7 +820,7 @@
         <v>570568</v>
       </c>
       <c r="R3" t="n">
-        <v>7108432</v>
+        <v>7108430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131742</v>
+        <v>122131776</v>
       </c>
       <c r="B4" t="n">
-        <v>90775</v>
+        <v>97139</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>885</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tajgaporing</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inonotopsis subiculosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570510</v>
+        <v>570525</v>
       </c>
       <c r="R4" t="n">
-        <v>7108431</v>
+        <v>7108433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122132202</v>
+        <v>122131802</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
         <v>570568</v>
       </c>
       <c r="R5" t="n">
-        <v>7108430</v>
+        <v>7108432</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131776</v>
+        <v>122131821</v>
       </c>
       <c r="B7" t="n">
-        <v>97139</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570525</v>
+        <v>570563</v>
       </c>
       <c r="R7" t="n">
-        <v>7108433</v>
+        <v>7108426</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58744-2022 artfynd.xlsx
+++ b/artfynd/A 58744-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131742</v>
+        <v>122131802</v>
       </c>
       <c r="B2" t="n">
-        <v>90775</v>
+        <v>79732</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>885</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tajgaporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Inonotopsis subiculosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570510</v>
+        <v>570568</v>
       </c>
       <c r="R2" t="n">
-        <v>7108431</v>
+        <v>7108432</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132202</v>
+        <v>122131760</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570568</v>
+        <v>570496</v>
       </c>
       <c r="R3" t="n">
-        <v>7108430</v>
+        <v>7108437</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131776</v>
+        <v>122132202</v>
       </c>
       <c r="B4" t="n">
-        <v>97139</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570525</v>
+        <v>570568</v>
       </c>
       <c r="R4" t="n">
-        <v>7108433</v>
+        <v>7108430</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131802</v>
+        <v>122131776</v>
       </c>
       <c r="B5" t="n">
-        <v>79727</v>
+        <v>97151</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570568</v>
+        <v>570525</v>
       </c>
       <c r="R5" t="n">
-        <v>7108432</v>
+        <v>7108433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131760</v>
+        <v>122131821</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570496</v>
+        <v>570563</v>
       </c>
       <c r="R6" t="n">
-        <v>7108437</v>
+        <v>7108426</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131821</v>
+        <v>122131742</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>90787</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>885</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgaporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inonotopsis subiculosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570563</v>
+        <v>570510</v>
       </c>
       <c r="R7" t="n">
-        <v>7108426</v>
+        <v>7108431</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58744-2022 artfynd.xlsx
+++ b/artfynd/A 58744-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131760</v>
+        <v>122131776</v>
       </c>
       <c r="B3" t="n">
-        <v>78651</v>
+        <v>97156</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570496</v>
+        <v>570525</v>
       </c>
       <c r="R3" t="n">
-        <v>7108437</v>
+        <v>7108433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132202</v>
+        <v>122131821</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570568</v>
+        <v>570563</v>
       </c>
       <c r="R4" t="n">
-        <v>7108430</v>
+        <v>7108426</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131776</v>
+        <v>122131742</v>
       </c>
       <c r="B5" t="n">
-        <v>97151</v>
+        <v>90794</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>885</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tajgaporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Inonotopsis subiculosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570525</v>
+        <v>570510</v>
       </c>
       <c r="R5" t="n">
-        <v>7108433</v>
+        <v>7108431</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131821</v>
+        <v>122132202</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570563</v>
+        <v>570568</v>
       </c>
       <c r="R6" t="n">
-        <v>7108426</v>
+        <v>7108430</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131742</v>
+        <v>122131760</v>
       </c>
       <c r="B7" t="n">
-        <v>90787</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>885</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tajgaporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Inonotopsis subiculosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570510</v>
+        <v>570496</v>
       </c>
       <c r="R7" t="n">
-        <v>7108431</v>
+        <v>7108437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58744-2022 artfynd.xlsx
+++ b/artfynd/A 58744-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131802</v>
+        <v>122131776</v>
       </c>
       <c r="B2" t="n">
-        <v>79732</v>
+        <v>97165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570568</v>
+        <v>570525</v>
       </c>
       <c r="R2" t="n">
-        <v>7108432</v>
+        <v>7108433</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131776</v>
+        <v>122132202</v>
       </c>
       <c r="B3" t="n">
-        <v>97156</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +784,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570525</v>
+        <v>570568</v>
       </c>
       <c r="R3" t="n">
-        <v>7108433</v>
+        <v>7108430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131821</v>
+        <v>122131760</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,11 +887,6 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570563</v>
+        <v>570496</v>
       </c>
       <c r="R4" t="n">
-        <v>7108426</v>
+        <v>7108437</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131742</v>
+        <v>122131802</v>
       </c>
       <c r="B5" t="n">
-        <v>90794</v>
+        <v>79733</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +978,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>885</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tajgaporing</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inonotopsis subiculosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570510</v>
+        <v>570568</v>
       </c>
       <c r="R5" t="n">
-        <v>7108431</v>
+        <v>7108432</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122132202</v>
+        <v>122131742</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>90799</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1075,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>885</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inonotopsis subiculosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570568</v>
+        <v>570510</v>
       </c>
       <c r="R6" t="n">
-        <v>7108430</v>
+        <v>7108431</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131760</v>
+        <v>122131821</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1203,11 +1178,6 @@
       <c r="E7" t="n">
         <v>6425</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570496</v>
+        <v>570563</v>
       </c>
       <c r="R7" t="n">
-        <v>7108437</v>
+        <v>7108426</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58744-2022 artfynd.xlsx
+++ b/artfynd/A 58744-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131776</v>
+        <v>122131742</v>
       </c>
       <c r="B2" t="n">
-        <v>97165</v>
+        <v>90812</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>885</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tajgaporing</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Inonotopsis subiculosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570525</v>
+        <v>570510</v>
       </c>
       <c r="R2" t="n">
-        <v>7108433</v>
+        <v>7108431</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +780,7 @@
         <v>122132202</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,6 +794,11 @@
       </c>
       <c r="E3" t="n">
         <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131760</v>
+        <v>122131802</v>
       </c>
       <c r="B4" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -885,16 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570496</v>
+        <v>570568</v>
       </c>
       <c r="R4" t="n">
-        <v>7108437</v>
+        <v>7108432</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131802</v>
+        <v>122131821</v>
       </c>
       <c r="B5" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -982,16 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570568</v>
+        <v>570563</v>
       </c>
       <c r="R5" t="n">
-        <v>7108432</v>
+        <v>7108426</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131742</v>
+        <v>122131760</v>
       </c>
       <c r="B6" t="n">
-        <v>90799</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1075,20 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>885</v>
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inonotopsis subiculosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570510</v>
+        <v>570496</v>
       </c>
       <c r="R6" t="n">
-        <v>7108431</v>
+        <v>7108437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131821</v>
+        <v>122131776</v>
       </c>
       <c r="B7" t="n">
-        <v>78652</v>
+        <v>97178</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1172,20 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570563</v>
+        <v>570525</v>
       </c>
       <c r="R7" t="n">
-        <v>7108426</v>
+        <v>7108433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58744-2022 artfynd.xlsx
+++ b/artfynd/A 58744-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131742</v>
+        <v>122131760</v>
       </c>
       <c r="B2" t="n">
-        <v>90812</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>885</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tajgaporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Inonotopsis subiculosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570510</v>
+        <v>570496</v>
       </c>
       <c r="R2" t="n">
-        <v>7108431</v>
+        <v>7108437</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132202</v>
+        <v>122131776</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>97191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570568</v>
+        <v>570525</v>
       </c>
       <c r="R3" t="n">
-        <v>7108430</v>
+        <v>7108433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131821</v>
+        <v>122132202</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570563</v>
+        <v>570568</v>
       </c>
       <c r="R5" t="n">
-        <v>7108426</v>
+        <v>7108430</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131760</v>
+        <v>122131821</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570496</v>
+        <v>570563</v>
       </c>
       <c r="R6" t="n">
-        <v>7108437</v>
+        <v>7108426</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131776</v>
+        <v>122131742</v>
       </c>
       <c r="B7" t="n">
-        <v>97178</v>
+        <v>90825</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>885</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tajgaporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Inonotopsis subiculosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570525</v>
+        <v>570510</v>
       </c>
       <c r="R7" t="n">
-        <v>7108433</v>
+        <v>7108431</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
